--- a/численные методы.xlsx
+++ b/численные методы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20d8967ec272c1da/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_AD4DF75460589B3ACB72848F3F9940C25BDEDD99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A4F1911-FB8F-4BE4-860C-E5EBCE571BC3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_AD4DF75460589B3ACB72848F3F9940C25BDEDD99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DABA0A8E-C8D8-4169-BD72-7FDA62F62A7C}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1716" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1716" windowWidth="17280" windowHeight="8964" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="бисекция" sheetId="1" r:id="rId1"/>
@@ -1867,7 +1867,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="12">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -1928,23 +1928,23 @@
       </c>
       <c r="B7" s="10">
         <f>B2</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C7" s="10">
         <f>B7^3-B7-1</f>
-        <v>5</v>
+        <v>0.875</v>
       </c>
       <c r="D7" s="10">
         <f>3*B7^2-1</f>
-        <v>11</v>
+        <v>5.75</v>
       </c>
       <c r="E7" s="10">
         <f>B7-C7/D7</f>
-        <v>1.5454545454545454</v>
+        <v>1.3478260869565217</v>
       </c>
       <c r="F7" s="10">
         <f>ABS(E7-B7)</f>
-        <v>0.45454545454545459</v>
+        <v>0.15217391304347827</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1954,23 +1954,23 @@
       </c>
       <c r="B8" s="10">
         <f>E7</f>
-        <v>1.5454545454545454</v>
+        <v>1.3478260869565217</v>
       </c>
       <c r="C8" s="10">
         <f>B8^3-B8-1</f>
-        <v>1.1457550713749058</v>
+        <v>0.10068217309114824</v>
       </c>
       <c r="D8" s="10">
         <f>3*B8^2-1</f>
-        <v>6.1652892561983466</v>
+        <v>4.4499054820415882</v>
       </c>
       <c r="E8" s="10">
         <f>B8-C8/D8</f>
-        <v>1.359614915915184</v>
+        <v>1.3252003989509069</v>
       </c>
       <c r="F8" s="10">
         <f>ABS(E8-B8)</f>
-        <v>0.1858396295393614</v>
+        <v>2.2625688005614819E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1980,23 +1980,23 @@
       </c>
       <c r="B9" s="10">
         <f t="shared" ref="B9:B13" si="1">E8</f>
-        <v>1.359614915915184</v>
+        <v>1.3252003989509069</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" ref="C9:C13" si="2">B9^3-B9-1</f>
-        <v>0.15370493448007472</v>
+        <v>2.0583619166634204E-3</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" ref="D9:D13" si="3">3*B9^2-1</f>
-        <v>4.5456581587371589</v>
+        <v>4.2684682921389285</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" ref="E9:E13" si="4">B9-C9/D9</f>
-        <v>1.325801345005845</v>
+        <v>1.3247181739990537</v>
       </c>
       <c r="F9" s="10">
         <f t="shared" ref="F9:F13" si="5">ABS(E9-B9)</f>
-        <v>3.3813570909339008E-2</v>
+        <v>4.8222495185323844E-4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2006,23 +2006,23 @@
       </c>
       <c r="B10" s="10">
         <f t="shared" si="1"/>
-        <v>1.325801345005845</v>
+        <v>1.3247181739990537</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>4.6249170478298574E-3</v>
+        <v>9.2437775967013636E-7</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>4.2732476192579227</v>
+        <v>4.264634721570161</v>
       </c>
       <c r="E10" s="10">
         <f t="shared" si="4"/>
-        <v>1.3247190494171253</v>
+        <v>1.3247179572447898</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="5"/>
-        <v>1.0822955887197505E-3</v>
+        <v>2.1675426387091079E-7</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2032,23 +2032,23 @@
       </c>
       <c r="B11" s="11">
         <f t="shared" si="1"/>
-        <v>1.3247190494171253</v>
+        <v>1.3247179572447898</v>
       </c>
       <c r="C11" s="11">
         <f t="shared" si="2"/>
-        <v>4.6577191092911363E-6</v>
+        <v>1.865174681370263E-13</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" si="3"/>
-        <v>4.2646416796658357</v>
+        <v>4.2646329987404261</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" si="4"/>
-        <v>1.3247179572458576</v>
+        <v>1.3247179572447461</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="5"/>
-        <v>1.0921712676470463E-6</v>
+        <v>4.3742787170231168E-14</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2058,15 +2058,15 @@
       </c>
       <c r="B12" s="10">
         <f t="shared" si="1"/>
-        <v>1.3247179572458576</v>
+        <v>1.3247179572447461</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>4.7404302705444934E-12</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>4.2646329987489136</v>
+        <v>4.2646329987400788</v>
       </c>
       <c r="E12" s="10">
         <f t="shared" si="4"/>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F12" s="10">
         <f t="shared" si="5"/>
-        <v>1.1115552922547067E-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
